--- a/main/StructureDefinition-ConsentTemplate.xlsx
+++ b/main/StructureDefinition-ConsentTemplate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="863">
   <si>
     <t>Property</t>
   </si>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -473,6 +473,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Questionnaire.extension:sourceDocument.id</t>
   </si>
   <si>
@@ -840,9 +844,6 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/signature-type|4.0.1</t>
-  </si>
-  <si>
     <t>Questionnaire.extension:signatureRequired.value[x].id</t>
   </si>
   <si>
@@ -1254,7 +1255,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1339,7 +1340,7 @@
     <t>Questionnaire.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1422,7 +1423,7 @@
     <t>Questionnaire.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Questionnaire|4.0.1)
+    <t xml:space="preserve">canonical(Questionnaire)
 </t>
   </si>
   <si>
@@ -1722,6 +1723,9 @@
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1775,7 +1779,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -2163,7 +2167,7 @@
     <t>Codes for questionnaires, groups and individual questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions</t>
   </si>
   <si>
     <t>Questionnaire.item.code.id</t>
@@ -2439,7 +2443,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringCodingQuantityReference(Resource|4.0.1)</t>
+decimalintegerdatedateTimetimestringCodingQuantityReference(Resource)</t>
   </si>
   <si>
     <t>Value for question comparison based on operator</t>
@@ -2451,7 +2455,7 @@
     <t>Allowed values to answer questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
   </si>
   <si>
     <t xml:space="preserve">que-7
@@ -2558,7 +2562,7 @@
     <t>Questionnaire.item.answerValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet|4.0.1)
+    <t xml:space="preserve">canonical(ValueSet)
 </t>
   </si>
   <si>
@@ -2600,7 +2604,7 @@
   </si>
   <si>
     <t>integer
-datetimestringCodingReference(Resource|4.0.1)</t>
+datetimestringCodingReference(Resource)</t>
   </si>
   <si>
     <t>Answer value</t>
@@ -2659,7 +2663,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource|4.0.1)</t>
+decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource)</t>
   </si>
   <si>
     <t>Actual value for initializing the question</t>
@@ -4208,7 +4212,7 @@
         <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -4228,10 +4232,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -4254,13 +4258,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4311,7 +4315,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -4329,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>21</v>
@@ -4343,14 +4347,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -4372,13 +4376,13 @@
         <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -4419,7 +4423,7 @@
         <v>136</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>21</v>
@@ -4428,7 +4432,7 @@
         <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -4446,7 +4450,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -4460,10 +4464,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4489,13 +4493,13 @@
         <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4503,7 +4507,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>21</v>
@@ -4545,7 +4549,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
@@ -4577,10 +4581,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4603,13 +4607,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4660,7 +4664,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4692,10 +4696,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4718,13 +4722,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4775,7 +4779,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4793,7 +4797,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -4807,14 +4811,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4836,13 +4840,13 @@
         <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4883,7 +4887,7 @@
         <v>136</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
@@ -4892,7 +4896,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4910,7 +4914,7 @@
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -4924,10 +4928,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4953,14 +4957,14 @@
         <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -4973,7 +4977,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -4985,13 +4989,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -5009,7 +5013,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -5027,7 +5031,7 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -5036,15 +5040,15 @@
         <v>21</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5070,14 +5074,14 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -5090,7 +5094,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -5126,7 +5130,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -5144,7 +5148,7 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -5158,10 +5162,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5184,19 +5188,19 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -5245,7 +5249,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -5263,7 +5267,7 @@
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -5272,15 +5276,15 @@
         <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5303,19 +5307,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -5328,7 +5332,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -5364,7 +5368,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -5382,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -5391,15 +5395,15 @@
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5422,19 +5426,19 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -5483,7 +5487,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5501,7 +5505,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -5515,10 +5519,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5541,19 +5545,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -5602,7 +5606,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5620,7 +5624,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -5634,10 +5638,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5660,17 +5664,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -5683,7 +5687,7 @@
         <v>21</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>21</v>
@@ -5719,7 +5723,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5737,7 +5741,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -5751,10 +5755,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5777,17 +5781,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -5836,7 +5840,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5854,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -5868,13 +5872,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
@@ -5896,16 +5900,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5964,10 +5968,10 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
@@ -5987,10 +5991,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6013,13 +6017,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6070,7 +6074,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6088,7 +6092,7 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -6102,10 +6106,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6176,7 +6180,7 @@
         <v>136</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>21</v>
@@ -6185,7 +6189,7 @@
         <v>137</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -6217,10 +6221,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6246,13 +6250,13 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6260,7 +6264,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>21</v>
@@ -6302,7 +6306,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -6334,10 +6338,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6360,13 +6364,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6393,11 +6397,11 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -6415,7 +6419,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6450,7 +6454,7 @@
         <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6473,13 +6477,13 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6530,7 +6534,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6548,7 +6552,7 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -6565,11 +6569,11 @@
         <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6591,13 +6595,13 @@
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6638,7 +6642,7 @@
         <v>136</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
@@ -6647,7 +6651,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6665,7 +6669,7 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -6824,13 +6828,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6881,7 +6885,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6899,7 +6903,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6942,13 +6946,13 @@
         <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6989,7 +6993,7 @@
         <v>136</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
@@ -6998,7 +7002,7 @@
         <v>137</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -7016,7 +7020,7 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -7175,7 +7179,7 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>293</v>
@@ -7409,7 +7413,7 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>309</v>
@@ -7645,7 +7649,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>327</v>
@@ -8326,7 +8330,7 @@
         <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8349,13 +8353,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8406,7 +8410,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8424,7 +8428,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -8441,7 +8445,7 @@
         <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8512,7 +8516,7 @@
         <v>136</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
@@ -8521,7 +8525,7 @@
         <v>137</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8556,7 +8560,7 @@
         <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8582,13 +8586,13 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8638,7 +8642,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>88</v>
@@ -8673,7 +8677,7 @@
         <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8696,13 +8700,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8753,7 +8757,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8792,7 +8796,7 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8820,7 +8824,7 @@
         <v>363</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>364</v>
@@ -9168,13 +9172,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9225,7 +9229,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9243,7 +9247,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -9264,7 +9268,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9286,13 +9290,13 @@
         <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9333,7 +9337,7 @@
         <v>136</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
@@ -9342,7 +9346,7 @@
         <v>137</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9360,7 +9364,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -9437,7 +9441,7 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y55" t="s" s="2">
         <v>390</v>
@@ -9519,7 +9523,7 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>395</v>
@@ -9556,7 +9560,7 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y56" t="s" s="2">
         <v>399</v>
@@ -9757,7 +9761,7 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>413</v>
@@ -10106,7 +10110,7 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>436</v>
@@ -10223,7 +10227,7 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>443</v>
@@ -10342,7 +10346,7 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>449</v>
@@ -10611,7 +10615,7 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y65" t="s" s="2">
         <v>465</v>
@@ -10847,7 +10851,7 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y67" t="s" s="2">
         <v>480</v>
@@ -10929,7 +10933,7 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>486</v>
@@ -11046,7 +11050,7 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>493</v>
@@ -11518,13 +11522,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11575,7 +11579,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11593,7 +11597,7 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -11614,7 +11618,7 @@
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11636,13 +11640,13 @@
         <v>133</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11683,7 +11687,7 @@
         <v>136</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>21</v>
@@ -11692,7 +11696,7 @@
         <v>137</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11710,7 +11714,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -11783,7 +11787,7 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
@@ -11863,13 +11867,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11920,7 +11924,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11938,7 +11942,7 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
@@ -11959,7 +11963,7 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11981,13 +11985,13 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12028,7 +12032,7 @@
         <v>136</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>21</v>
@@ -12037,7 +12041,7 @@
         <v>137</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12055,7 +12059,7 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -12214,7 +12218,7 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>293</v>
@@ -12448,7 +12452,7 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>309</v>
@@ -12799,13 +12803,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12856,7 +12860,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12874,7 +12878,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -12895,7 +12899,7 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12917,13 +12921,13 @@
         <v>133</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12964,7 +12968,7 @@
         <v>136</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>21</v>
@@ -12973,7 +12977,7 @@
         <v>137</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12991,7 +12995,7 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -13031,7 +13035,7 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>543</v>
@@ -13183,13 +13187,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y87" t="s" s="2">
         <v>552</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -13207,7 +13211,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13239,10 +13243,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13268,13 +13272,13 @@
         <v>375</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13324,7 +13328,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13356,10 +13360,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13382,16 +13386,16 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13441,7 +13445,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13473,10 +13477,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13499,16 +13503,16 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13534,13 +13538,13 @@
         <v>21</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -13558,7 +13562,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13573,7 +13577,7 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>440</v>
@@ -13590,10 +13594,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13619,13 +13623,13 @@
         <v>508</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13675,7 +13679,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13690,13 +13694,13 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>382</v>
@@ -13707,14 +13711,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13736,14 +13740,14 @@
         <v>508</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13792,7 +13796,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13807,7 +13811,7 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>440</v>
@@ -13824,10 +13828,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13850,16 +13854,16 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13909,7 +13913,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13924,10 +13928,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
@@ -13941,10 +13945,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13967,19 +13971,19 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -14028,7 +14032,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14043,10 +14047,10 @@
         <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>21</v>
@@ -14060,10 +14064,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14089,16 +14093,16 @@
         <v>421</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -14147,7 +14151,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14162,7 +14166,7 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>440</v>
@@ -14179,10 +14183,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14208,14 +14212,14 @@
         <v>270</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -14240,11 +14244,11 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -14262,7 +14266,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14280,7 +14284,7 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -14294,10 +14298,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14320,13 +14324,13 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14377,7 +14381,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14395,7 +14399,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
@@ -14409,14 +14413,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14438,13 +14442,13 @@
         <v>133</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14485,7 +14489,7 @@
         <v>136</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>21</v>
@@ -14494,7 +14498,7 @@
         <v>137</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14512,7 +14516,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>21</v>
@@ -14526,10 +14530,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14645,10 +14649,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14671,7 +14675,7 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>293</v>
@@ -14762,10 +14766,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14879,10 +14883,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14905,7 +14909,7 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>309</v>
@@ -14996,10 +15000,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15115,10 +15119,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15141,16 +15145,16 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15200,7 +15204,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15209,16 +15213,16 @@
         <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>21</v>
@@ -15232,10 +15236,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15258,13 +15262,13 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15315,7 +15319,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15333,7 +15337,7 @@
         <v>21</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
@@ -15347,10 +15351,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15428,7 +15432,7 @@
         <v>137</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15460,13 +15464,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="B107" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="C107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>21</v>
@@ -15476,7 +15480,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>89</v>
@@ -15488,16 +15492,16 @@
         <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15547,7 +15551,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15556,10 +15560,10 @@
         <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>21</v>
@@ -15579,13 +15583,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>21</v>
@@ -15607,7 +15611,7 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>143</v>
@@ -15664,7 +15668,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15676,7 +15680,7 @@
         <v>145</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>21</v>
@@ -15696,10 +15700,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15722,13 +15726,13 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15779,7 +15783,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15797,7 +15801,7 @@
         <v>21</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -15811,10 +15815,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15885,7 +15889,7 @@
         <v>136</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>21</v>
@@ -15894,7 +15898,7 @@
         <v>137</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15926,10 +15930,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15955,13 +15959,13 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15969,7 +15973,7 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>21</v>
@@ -16011,7 +16015,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>88</v>
@@ -16043,10 +16047,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16069,13 +16073,13 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16126,7 +16130,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16158,10 +16162,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16184,13 +16188,13 @@
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16241,7 +16245,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16259,7 +16263,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
@@ -16273,14 +16277,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16302,13 +16306,13 @@
         <v>133</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16349,7 +16353,7 @@
         <v>136</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>21</v>
@@ -16358,7 +16362,7 @@
         <v>137</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16376,7 +16380,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
@@ -16390,10 +16394,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16416,7 +16420,7 @@
         <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>543</v>
@@ -16507,10 +16511,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16568,13 +16572,13 @@
         <v>21</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y116" t="s" s="2">
         <v>552</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
@@ -16592,7 +16596,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16624,10 +16628,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16653,13 +16657,13 @@
         <v>375</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16709,7 +16713,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16741,10 +16745,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16767,16 +16771,16 @@
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16826,7 +16830,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16858,10 +16862,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>340</v>
@@ -16943,7 +16947,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16975,10 +16979,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>344</v>
@@ -17060,7 +17064,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17092,13 +17096,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>21</v>
@@ -17120,7 +17124,7 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>342</v>
@@ -17177,7 +17181,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17209,13 +17213,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>21</v>
@@ -17237,13 +17241,13 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17294,7 +17298,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17326,14 +17330,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17355,13 +17359,13 @@
         <v>133</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>364</v>
@@ -17413,7 +17417,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17445,10 +17449,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17471,19 +17475,19 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -17532,7 +17536,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>88</v>
@@ -17550,7 +17554,7 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>21</v>
@@ -17564,10 +17568,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17593,16 +17597,16 @@
         <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
@@ -17651,7 +17655,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17669,7 +17673,7 @@
         <v>21</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>21</v>
@@ -17683,10 +17687,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17712,16 +17716,16 @@
         <v>270</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17746,13 +17750,13 @@
         <v>21</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
@@ -17770,7 +17774,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17779,7 +17783,7 @@
         <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
@@ -17788,7 +17792,7 @@
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>21</v>
@@ -17802,10 +17806,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17828,13 +17832,13 @@
         <v>21</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17885,7 +17889,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17903,7 +17907,7 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
@@ -17917,14 +17921,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17946,13 +17950,13 @@
         <v>133</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17993,7 +17997,7 @@
         <v>136</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>21</v>
@@ -18002,7 +18006,7 @@
         <v>137</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18020,7 +18024,7 @@
         <v>21</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>21</v>
@@ -18034,10 +18038,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18153,10 +18157,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18179,7 +18183,7 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L130" t="s" s="2">
         <v>293</v>
@@ -18270,10 +18274,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18387,10 +18391,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18413,7 +18417,7 @@
         <v>89</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>309</v>
@@ -18504,10 +18508,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18623,14 +18627,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18649,19 +18653,19 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -18710,7 +18714,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18728,7 +18732,7 @@
         <v>21</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>21</v>
@@ -18742,10 +18746,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18768,16 +18772,16 @@
         <v>21</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18827,7 +18831,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18859,10 +18863,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18885,13 +18889,13 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18942,7 +18946,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18974,10 +18978,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19055,7 +19059,7 @@
         <v>137</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19087,13 +19091,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="B138" t="s" s="2">
-        <v>714</v>
-      </c>
       <c r="C138" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -19103,7 +19107,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>21</v>
@@ -19115,13 +19119,13 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19172,7 +19176,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19181,16 +19185,16 @@
         <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>21</v>
@@ -19204,13 +19208,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
@@ -19220,7 +19224,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>21</v>
@@ -19232,13 +19236,13 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19289,7 +19293,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19298,16 +19302,16 @@
         <v>81</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>21</v>
@@ -19321,10 +19325,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19347,13 +19351,13 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19377,7 +19381,7 @@
         <v>21</v>
       </c>
       <c r="W140" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="X140" t="s" s="2">
         <v>21</v>
@@ -19404,7 +19408,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19436,10 +19440,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19465,16 +19469,16 @@
         <v>108</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>21</v>
@@ -19499,13 +19503,13 @@
         <v>21</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>21</v>
@@ -19523,7 +19527,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>88</v>
@@ -19541,7 +19545,7 @@
         <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>21</v>
@@ -19555,10 +19559,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19581,19 +19585,19 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -19642,7 +19646,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19654,13 +19658,13 @@
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>21</v>
@@ -19674,10 +19678,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19700,13 +19704,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19757,7 +19761,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19775,7 +19779,7 @@
         <v>21</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>21</v>
@@ -19789,10 +19793,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19870,7 +19874,7 @@
         <v>137</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19902,13 +19906,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="B145" t="s" s="2">
-        <v>747</v>
-      </c>
       <c r="C145" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>21</v>
@@ -19930,7 +19934,7 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>143</v>
@@ -19987,7 +19991,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19999,7 +20003,7 @@
         <v>145</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>21</v>
@@ -20019,10 +20023,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20045,13 +20049,13 @@
         <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20102,7 +20106,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20120,7 +20124,7 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>21</v>
@@ -20134,14 +20138,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20163,13 +20167,13 @@
         <v>133</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20210,7 +20214,7 @@
         <v>136</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>21</v>
@@ -20219,7 +20223,7 @@
         <v>137</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20237,7 +20241,7 @@
         <v>21</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>21</v>
@@ -20251,10 +20255,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20280,13 +20284,13 @@
         <v>102</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20294,7 +20298,7 @@
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>21</v>
@@ -20336,7 +20340,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>88</v>
@@ -20368,10 +20372,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20394,13 +20398,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20451,7 +20455,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20483,10 +20487,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20509,13 +20513,13 @@
         <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20566,7 +20570,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20584,7 +20588,7 @@
         <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>21</v>
@@ -20598,14 +20602,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -20627,13 +20631,13 @@
         <v>133</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20674,7 +20678,7 @@
         <v>136</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>21</v>
@@ -20683,7 +20687,7 @@
         <v>137</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20701,7 +20705,7 @@
         <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>21</v>
@@ -20715,10 +20719,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20741,7 +20745,7 @@
         <v>89</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>543</v>
@@ -20832,10 +20836,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20893,13 +20897,13 @@
         <v>21</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y153" t="s" s="2">
         <v>552</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>21</v>
@@ -20917,7 +20921,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20949,10 +20953,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20978,13 +20982,13 @@
         <v>375</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21034,7 +21038,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21066,10 +21070,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21092,16 +21096,16 @@
         <v>89</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21151,7 +21155,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21183,14 +21187,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21212,13 +21216,13 @@
         <v>133</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O156" t="s" s="2">
         <v>364</v>
@@ -21270,7 +21274,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21302,10 +21306,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21328,16 +21332,16 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21387,7 +21391,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>88</v>
@@ -21405,7 +21409,7 @@
         <v>21</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>21</v>
@@ -21419,10 +21423,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21448,10 +21452,10 @@
         <v>108</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21478,13 +21482,13 @@
         <v>21</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>21</v>
@@ -21502,7 +21506,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>88</v>
@@ -21520,7 +21524,7 @@
         <v>21</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>21</v>
@@ -21534,10 +21538,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21560,13 +21564,13 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21593,13 +21597,13 @@
         <v>21</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
@@ -21617,7 +21621,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>88</v>
@@ -21626,7 +21630,7 @@
         <v>88</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>100</v>
@@ -21635,7 +21639,7 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>21</v>
@@ -21649,10 +21653,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21678,13 +21682,13 @@
         <v>108</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21710,13 +21714,13 @@
         <v>21</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>21</v>
@@ -21734,7 +21738,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21743,7 +21747,7 @@
         <v>88</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>100</v>
@@ -21752,7 +21756,7 @@
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>21</v>
@@ -21766,10 +21770,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21795,20 +21799,20 @@
         <v>317</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q161" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="R161" t="s" s="2">
         <v>21</v>
@@ -21853,7 +21857,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21862,7 +21866,7 @@
         <v>88</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>100</v>
@@ -21871,7 +21875,7 @@
         <v>21</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>21</v>
@@ -21885,10 +21889,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21914,76 +21918,76 @@
         <v>317</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="P162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q162" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="R162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF162" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="M162" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q162" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="R162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF162" t="s" s="2">
+      <c r="AG162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI162" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>100</v>
@@ -21992,7 +21996,7 @@
         <v>21</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>21</v>
@@ -22006,10 +22010,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22035,16 +22039,16 @@
         <v>317</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -22093,7 +22097,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22102,7 +22106,7 @@
         <v>88</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>100</v>
@@ -22111,7 +22115,7 @@
         <v>21</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>21</v>
@@ -22125,10 +22129,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22151,16 +22155,16 @@
         <v>21</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22210,7 +22214,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22219,7 +22223,7 @@
         <v>88</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>100</v>
@@ -22228,7 +22232,7 @@
         <v>21</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>21</v>
@@ -22242,10 +22246,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22268,16 +22272,16 @@
         <v>21</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22327,7 +22331,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22336,7 +22340,7 @@
         <v>88</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>100</v>
@@ -22345,7 +22349,7 @@
         <v>21</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>21</v>
@@ -22359,10 +22363,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22385,16 +22389,16 @@
         <v>21</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22444,7 +22448,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22453,7 +22457,7 @@
         <v>81</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>100</v>
@@ -22462,7 +22466,7 @@
         <v>21</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>21</v>
@@ -22476,10 +22480,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22502,13 +22506,13 @@
         <v>21</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22559,7 +22563,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22577,7 +22581,7 @@
         <v>21</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>21</v>
@@ -22591,14 +22595,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -22620,13 +22624,13 @@
         <v>133</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22676,7 +22680,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22694,7 +22698,7 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>21</v>
@@ -22708,14 +22712,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -22737,13 +22741,13 @@
         <v>133</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O169" t="s" s="2">
         <v>364</v>
@@ -22795,7 +22799,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22827,10 +22831,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22853,16 +22857,16 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -22888,13 +22892,13 @@
         <v>21</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>21</v>
@@ -22912,7 +22916,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>88</v>
@@ -22930,7 +22934,7 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>21</v>
@@ -22944,10 +22948,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22973,20 +22977,20 @@
         <v>317</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q171" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="R171" t="s" s="2">
         <v>21</v>
@@ -23031,7 +23035,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23049,7 +23053,7 @@
         <v>21</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>21</v>
@@ -23063,10 +23067,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23089,19 +23093,19 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -23150,7 +23154,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23159,7 +23163,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>100</v>
@@ -23168,7 +23172,7 @@
         <v>21</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>21</v>
@@ -23182,10 +23186,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23208,13 +23212,13 @@
         <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23265,7 +23269,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23283,7 +23287,7 @@
         <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>21</v>
@@ -23297,14 +23301,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -23326,13 +23330,13 @@
         <v>133</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23382,7 +23386,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23400,7 +23404,7 @@
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>21</v>
@@ -23414,14 +23418,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23443,13 +23447,13 @@
         <v>133</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O175" t="s" s="2">
         <v>364</v>
@@ -23501,7 +23505,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23533,10 +23537,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23559,16 +23563,16 @@
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -23594,13 +23598,13 @@
         <v>21</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>21</v>
@@ -23618,7 +23622,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>88</v>
@@ -23636,7 +23640,7 @@
         <v>21</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>21</v>
@@ -23650,10 +23654,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23679,16 +23683,16 @@
         <v>82</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
@@ -23737,7 +23741,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23746,7 +23750,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>100</v>
@@ -23755,7 +23759,7 @@
         <v>21</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>21</v>
